--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_54_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_54_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3255</v>
+        <v>5.6622</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0765</v>
+        <v>6.3124</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.751</v>
+        <v>-0.6502</v>
       </c>
       <c r="G2" t="n">
         <v>2.3097</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9282</v>
+        <v>1.265</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3541</v>
+        <v>0.59</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5742</v>
+        <v>0.675</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0048</v>
+        <v>1.5912</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8462</v>
+        <v>3.567</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8414</v>
+        <v>-1.9758</v>
       </c>
       <c r="G3" t="n">
         <v>1.1432</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7714</v>
+        <v>0.3578</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6097</v>
+        <v>0.3306</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1617</v>
+        <v>0.0272</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="E4" t="n">
         <v>0.6261</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.544</v>
+        <v>-0.6112</v>
       </c>
       <c r="G4" t="n">
         <v>-0.329</v>
@@ -766,13 +766,13 @@
         <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0527</v>
+        <v>-0.1199</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4161</v>
+        <v>-0.6012</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8069</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3909</v>
+        <v>0.3237</v>
       </c>
       <c r="G5" t="n">
         <v>-2.745</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.883</v>
+        <v>0.6978</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2047</v>
+        <v>0.0868</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6783</v>
+        <v>0.6111</v>
       </c>
       <c r="V5" t="n">
         <v>1.214</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.772</v>
+        <v>-1.3364</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4475</v>
+        <v>-1.012</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3244</v>
+        <v>-0.3245</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.7188</v>
+        <v>-0.1582</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.347</v>
+        <v>-2.1824</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3718</v>
+        <v>2.0243</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7144</v>
+        <v>0.7529</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7674</v>
+        <v>-2.275</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.947</v>
+        <v>3.0279</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0044</v>
+        <v>-0.9111</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5796</v>
+        <v>0.0926</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4248</v>
+        <v>-1.0037</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8024</v>
+        <v>1.2856</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1404</v>
+        <v>0.5546</v>
       </c>
       <c r="U6" t="n">
-        <v>0.662</v>
+        <v>0.731</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1917</v>
+        <v>-1.4373</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7328</v>
+        <v>-0.6088</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4589</v>
+        <v>-0.8285</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1582</v>
+        <v>-3.7188</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1824</v>
+        <v>-2.347</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0243</v>
+        <v>-1.3718</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7529</v>
+        <v>-2.7144</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.275</v>
+        <v>-1.7674</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0279</v>
+        <v>-0.947</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9111</v>
+        <v>-1.0044</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0926</v>
+        <v>-0.5796</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0037</v>
+        <v>-0.4248</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4304</v>
+        <v>1.1371</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8338</v>
+        <v>0.9792</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5966</v>
+        <v>0.1579</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4759</v>
+        <v>-1.6027</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2902</v>
+        <v>-0.7023</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8143</v>
+        <v>-0.9004</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7441</v>
+        <v>-3.7545</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8847</v>
+        <v>-1.4658</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1406</v>
+        <v>-2.2887</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4687</v>
+        <v>-1.67</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5055</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-2.2854</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2755</v>
+        <v>-2.0845</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-2.0813</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1038</v>
+        <v>-0.0033</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5698</v>
+        <v>0.6183</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3383</v>
+        <v>0.8259</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2315</v>
+        <v>-0.2076</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3466</v>
+        <v>-1.7125</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7304</v>
+        <v>-2.762</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6162</v>
+        <v>1.0495</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9897</v>
+        <v>-1.7441</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6447</v>
+        <v>-1.8847</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3451</v>
+        <v>0.1406</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6636</v>
+        <v>-1.4687</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9509</v>
+        <v>-1.5055</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3261</v>
+        <v>-0.2755</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6938</v>
+        <v>-0.3792</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6323</v>
+        <v>0.1038</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0527</v>
+        <v>0.3332</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0668</v>
+        <v>-0.1336</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0141</v>
+        <v>0.4668</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4517</v>
+        <v>-2.1779</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2488</v>
+        <v>-1.4945</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2029</v>
+        <v>-0.6834</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7545</v>
+        <v>-2.9897</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4658</v>
+        <v>-1.6447</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2887</v>
+        <v>-1.3451</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.67</v>
+        <v>-1.6636</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6153999999999999</v>
+        <v>-0.9509</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2854</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0845</v>
+        <v>-1.3261</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0813</v>
+        <v>-0.6938</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0033</v>
+        <v>-0.6323</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2306</v>
+        <v>0.116</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2794</v>
+        <v>0.1691</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.51</v>
+        <v>-0.0532</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4933</v>
+        <v>-4.3</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3825</v>
+        <v>-3.9539</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1108</v>
+        <v>-0.3461</v>
       </c>
       <c r="G11" t="n">
         <v>-4.014</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2166</v>
+        <v>0.4099</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>0.1772</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4679</v>
+        <v>0.2326</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.06</v>
+        <v>-4.5216</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2808</v>
+        <v>-5.0449</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2208</v>
+        <v>0.5232</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0122</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0145</v>
+        <v>0.5239</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2047</v>
+        <v>0.4406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2192</v>
+        <v>0.0833</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.7949</v>
+        <v>-10.4213</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.371099999999999</v>
+        <v>-5.9978</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.4236</v>
+        <v>-4.423699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-17.0126</v>
@@ -1444,7 +1444,7 @@
         <v>-1.875000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.9616</v>
+        <v>-2.961600000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.0867</v>
@@ -1468,13 +1468,13 @@
         <v>12.7575</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2513</v>
+        <v>6.6247</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5802</v>
+        <v>3.953599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.671200000000001</v>
+        <v>2.6709</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1328</v>
+        <v>6.5881</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6054</v>
+        <v>6.7234</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4726</v>
+        <v>-0.1352</v>
       </c>
       <c r="G14" t="n">
         <v>11.6795</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5288</v>
+        <v>-1.0734</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9392</v>
+        <v>-0.6018</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4665</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2767</v>
+        <v>2.6002</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2186</v>
+        <v>0.9113</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0581</v>
+        <v>1.6888</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1499</v>
+        <v>1.9443</v>
       </c>
       <c r="H15" t="n">
-        <v>0.546</v>
+        <v>1.7166</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6959</v>
+        <v>0.2276</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4434</v>
+        <v>1.5727</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2961</v>
+        <v>1.4991</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1472</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5933</v>
+        <v>0.3715</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2499</v>
+        <v>0.2175</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8431</v>
+        <v>0.154</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7487</v>
+        <v>-0.2693</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2571</v>
+        <v>-0.0351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4916</v>
+        <v>-0.2341</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2412</v>
+        <v>2.1924</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9113</v>
+        <v>0.1412</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3299</v>
+        <v>2.0512</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9443</v>
+        <v>0.8354</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7166</v>
+        <v>0.8691</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2276</v>
+        <v>-0.0337</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5727</v>
+        <v>0.2639</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4991</v>
+        <v>0.6624</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>-0.3984</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3715</v>
+        <v>0.5715</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2175</v>
+        <v>0.2067</v>
       </c>
       <c r="O16" t="n">
-        <v>0.154</v>
+        <v>0.3648</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6282</v>
+        <v>-0.0373</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.593</v>
+        <v>-0.0022</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9304</v>
+        <v>0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3907</v>
+        <v>1.8568</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0696</v>
+        <v>0.0483</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4603</v>
+        <v>1.8084</v>
       </c>
       <c r="G17" t="n">
         <v>2.7014</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6329</v>
+        <v>-1.1668</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0433</v>
+        <v>-0.6952</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2044</v>
+        <v>1.4294</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3306</v>
+        <v>0.4493</v>
       </c>
       <c r="F18" t="n">
-        <v>1.535</v>
+        <v>0.9801</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8354</v>
+        <v>-0.1499</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8691</v>
+        <v>0.546</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0337</v>
+        <v>-0.6959</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2639</v>
+        <v>0.4434</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6624</v>
+        <v>0.2961</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3984</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5715</v>
+        <v>-0.5933</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2067</v>
+        <v>0.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3648</v>
+        <v>-0.8431</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0253</v>
+        <v>0.9014</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.507</v>
+        <v>0.4878</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5184</v>
+        <v>0.4136</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0537</v>
+        <v>0.9529</v>
       </c>
       <c r="E19" t="n">
         <v>0.433</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6207</v>
+        <v>0.5199</v>
       </c>
       <c r="G19" t="n">
         <v>0.8222</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2315</v>
+        <v>0.1307</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4942</v>
+        <v>0.7251</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3013</v>
+        <v>0.4193</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1929</v>
+        <v>0.3058</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2061</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7635</v>
+        <v>-0.5327</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.174</v>
+        <v>-0.0611</v>
       </c>
       <c r="V20" t="n">
         <v>0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4065</v>
+        <v>-0.3158</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9999</v>
+        <v>-1.764</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5933</v>
+        <v>1.4481</v>
       </c>
       <c r="G22" t="n">
         <v>0.7654</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0275</v>
+        <v>-0.9368</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.8017</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0101</v>
+        <v>-0.1351</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0385</v>
+        <v>-0.7421</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8504</v>
+        <v>0.5658</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1881</v>
+        <v>-1.3079</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.54</v>
+        <v>0.1404</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.1909</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0301</v>
+        <v>0.3312</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.426</v>
+        <v>1.0374</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9341</v>
+        <v>0.0203</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4919</v>
+        <v>1.0171</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8861</v>
+        <v>-0.897</v>
       </c>
       <c r="N23" t="n">
-        <v>0.364</v>
+        <v>-0.2112</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5221</v>
+        <v>-0.6859</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1428</v>
+        <v>-0.5061</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2715</v>
+        <v>-0.4716</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4143</v>
+        <v>-0.0345</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8197</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3558</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3426</v>
+        <v>-0.9656</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4478</v>
+        <v>-0.9683</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7904</v>
+        <v>0.0028</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1404</v>
+        <v>-0.54</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1909</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3312</v>
+        <v>0.0301</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0374</v>
+        <v>-1.426</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0203</v>
+        <v>-0.9341</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0171</v>
+        <v>-0.4919</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.897</v>
+        <v>0.8861</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2112</v>
+        <v>0.364</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6859</v>
+        <v>0.5221</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1066</v>
+        <v>-0.0698</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5895</v>
+        <v>0.1535</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5171</v>
+        <v>-0.2234</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0722</v>
+        <v>-0.8197</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3686</v>
+        <v>-1.3248</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2433</v>
+        <v>-2.5356</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8747</v>
+        <v>1.2108</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1371</v>
@@ -2404,13 +2404,13 @@
         <v>2.7834</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3759</v>
+        <v>-0.3321</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.187</v>
+        <v>-0.4793</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1889</v>
+        <v>0.1472</v>
       </c>
       <c r="V25" t="n">
         <v>1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.7948</v>
+        <v>13.1539</v>
       </c>
       <c r="E26" t="n">
-        <v>4.423599999999999</v>
+        <v>4.4237</v>
       </c>
       <c r="F26" t="n">
-        <v>6.3711</v>
+        <v>8.7301</v>
       </c>
       <c r="G26" t="n">
         <v>17.0128</v>
@@ -2458,7 +2458,7 @@
         <v>15.1379</v>
       </c>
       <c r="K26" t="n">
-        <v>7.4765</v>
+        <v>7.476499999999999</v>
       </c>
       <c r="L26" t="n">
         <v>7.6612</v>
@@ -2473,7 +2473,7 @@
         <v>-1.0865</v>
       </c>
       <c r="P26" t="n">
-        <v>2.319499999999999</v>
+        <v>2.3195</v>
       </c>
       <c r="Q26" t="n">
         <v>-12.7575</v>
@@ -2482,13 +2482,13 @@
         <v>15.0771</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.2513</v>
+        <v>-3.892199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.670800000000001</v>
+        <v>-2.671</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.5803</v>
+        <v>-1.2212</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2862</v>
